--- a/3-IndustrialProcesses/FoodAndBeverage/Brewery/Documents/Brewery_V0_rs_qt.xlsx
+++ b/3-IndustrialProcesses/FoodAndBeverage/Brewery/Documents/Brewery_V0_rs_qt.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">dTmin/2 = 5 K for liquid streams and 2 K for wort evaporation and vapour condensation; isothermal streams have a 0.1 K span.</t>
   </si>
   <si>
-    <t xml:space="preserve">Corrections to the source (pasteurisation at 70 C, whirlpool make-up water, dilution water) are listed in the handout, section Data basis.</t>
+    <t xml:space="preserve">Corrections to the source (pasteurisation at 70 C, whirlpool make-up water, dilution water) are listed in the case study, section Data basis.</t>
   </si>
   <si>
     <t xml:space="preserve">Utilities (steam, hot water, glycol-water, ammonia refrigeration, cooling water) are not part of the process data.</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">Reference targets for the 27 streams of the qt sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">Problem-table results with the dTmin/2 of each stream, given as values to check your own calculation.</t>
+    <t xml:space="preserve">Problem-table results with the dTmin/2 of each stream.</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity</t>

--- a/3-IndustrialProcesses/FoodAndBeverage/Brewery/Documents/Brewery_V0_rs_qt.xlsx
+++ b/3-IndustrialProcesses/FoodAndBeverage/Brewery/Documents/Brewery_V0_rs_qt.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">h/y</t>
   </si>
   <si>
-    <t xml:space="preserve">IPESE ROSMOSE brewery model (op_time)</t>
+    <t xml:space="preserve">Bhatnagar et al. (manuscript), op_time</t>
   </si>
   <si>
     <t xml:space="preserve">Reference flow of beer</t>
